--- a/result/szenarien_pivot.xlsx
+++ b/result/szenarien_pivot.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$865</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$997</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -544,7 +544,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -652,7 +652,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -868,7 +868,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -976,7 +976,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -1156,7 +1156,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -1264,7 +1264,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -1336,7 +1336,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -1408,7 +1408,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -1480,7 +1480,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -1552,7 +1552,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -1732,7 +1732,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -1804,7 +1804,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -1948,7 +1948,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -2020,7 +2020,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -2056,7 +2056,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -2128,7 +2128,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -2164,7 +2164,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2182,7 +2182,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -2272,7 +2272,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -2308,7 +2308,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -2344,7 +2344,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -2380,7 +2380,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -2488,7 +2488,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -2506,7 +2506,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -2524,7 +2524,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -2542,7 +2542,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -2560,7 +2560,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -2596,7 +2596,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -2632,7 +2632,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -2704,7 +2704,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -2776,7 +2776,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -2812,7 +2812,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -2884,7 +2884,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -2920,7 +2920,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -2956,7 +2956,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -3028,7 +3028,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -3100,7 +3100,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -3136,7 +3136,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -3172,7 +3172,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -3244,7 +3244,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -3280,7 +3280,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -3316,7 +3316,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -3388,7 +3388,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -3424,7 +3424,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -3532,7 +3532,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -3568,7 +3568,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -3640,7 +3640,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -3676,7 +3676,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -3712,7 +3712,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -3748,7 +3748,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -3784,7 +3784,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -3820,7 +3820,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -3892,7 +3892,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -3928,7 +3928,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -3964,7 +3964,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -4000,7 +4000,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -4036,7 +4036,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -4072,7 +4072,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -4144,7 +4144,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -4180,7 +4180,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -4216,7 +4216,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -4324,7 +4324,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -4396,7 +4396,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -4468,7 +4468,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -4504,7 +4504,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -4522,7 +4522,7 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -4576,7 +4576,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -4612,7 +4612,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -4648,7 +4648,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -4756,7 +4756,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -4792,7 +4792,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -4864,7 +4864,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -4936,7 +4936,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -4972,7 +4972,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -5026,7 +5026,7 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -5044,7 +5044,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -5080,7 +5080,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -5116,7 +5116,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -5188,7 +5188,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -5260,7 +5260,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -5296,7 +5296,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -5332,7 +5332,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -5368,7 +5368,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -5386,7 +5386,7 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -5404,7 +5404,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -5458,7 +5458,7 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -5476,7 +5476,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -5494,7 +5494,7 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -5512,7 +5512,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -5530,7 +5530,7 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -5548,7 +5548,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -5584,7 +5584,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -5620,7 +5620,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -5638,7 +5638,7 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -5692,7 +5692,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -5728,7 +5728,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -5764,7 +5764,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -5800,7 +5800,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -5836,7 +5836,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -5872,7 +5872,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -5908,7 +5908,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -5944,7 +5944,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -5962,7 +5962,7 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -5980,7 +5980,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -6016,7 +6016,7 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -6034,7 +6034,7 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -6052,7 +6052,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -6124,7 +6124,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -6196,7 +6196,7 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -6232,7 +6232,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -6268,7 +6268,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -6304,7 +6304,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -6322,7 +6322,7 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
@@ -6340,7 +6340,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
@@ -6376,7 +6376,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
@@ -6412,7 +6412,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
@@ -6484,7 +6484,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
@@ -6520,7 +6520,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
@@ -6556,7 +6556,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
@@ -6592,7 +6592,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
@@ -6628,7 +6628,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
@@ -6664,7 +6664,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
@@ -6700,7 +6700,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
@@ -6736,7 +6736,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
@@ -6772,7 +6772,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
@@ -6808,7 +6808,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
@@ -6844,7 +6844,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
@@ -6880,7 +6880,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
@@ -6916,7 +6916,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -6934,7 +6934,7 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
@@ -6952,7 +6952,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -6970,7 +6970,7 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
@@ -6988,7 +6988,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
@@ -7024,7 +7024,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
@@ -7060,7 +7060,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -7078,7 +7078,7 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
@@ -7132,7 +7132,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
@@ -7168,7 +7168,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
@@ -16057,8 +16057,2384 @@
         <v>2.29</v>
       </c>
     </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C866" s="3" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="D866" s="3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B867" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C867" s="5" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D867" s="5" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C868" s="3" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="D868" s="3" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B869" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C869" s="5" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="D869" s="5" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C870" s="3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="D870" s="3" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B871" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C871" s="5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D871" s="5" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C872" s="3" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="D872" s="3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B873" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C873" s="5" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D873" s="5" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C874" s="3" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="D874" s="3" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B875" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C875" s="5" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="D875" s="5" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C876" s="3" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="D876" s="3" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B877" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C877" s="5" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="D877" s="5" t="n">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C878" s="3" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="D878" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B879" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C879" s="5" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="D879" s="5" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C880" s="3" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="D880" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B881" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C881" s="5" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="D881" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C882" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D882" s="3" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B883" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C883" s="5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D883" s="5" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C884" s="3" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="D884" s="3" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B885" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C885" s="5" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="D885" s="5" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C886" s="3" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="D886" s="3" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B887" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C887" s="5" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="D887" s="5" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C888" s="3" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="D888" s="3" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B889" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C889" s="5" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="D889" s="5" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C890" s="3" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="D890" s="3" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B891" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C891" s="5" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="D891" s="5" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C892" s="3" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="D892" s="3" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B893" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C893" s="5" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="D893" s="5" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C894" s="3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="D894" s="3" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B895" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C895" s="5" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="D895" s="5" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C896" s="3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="D896" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B897" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C897" s="5" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="D897" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C898" s="3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="D898" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B899" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C899" s="5" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="D899" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C900" s="3" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="D900" s="3" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B901" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C901" s="5" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="D901" s="5" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C902" s="3" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="D902" s="3" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B903" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C903" s="5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="D903" s="5" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C904" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D904" s="3" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B905" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C905" s="5" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D905" s="5" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C906" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="D906" s="3" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B907" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C907" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="D907" s="5" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C908" s="3" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="D908" s="3" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B909" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C909" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="D909" s="5" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C910" s="3" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="D910" s="3" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B911" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C911" s="5" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="D911" s="5" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C912" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D912" s="3" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B913" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C913" s="5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D913" s="5" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C914" s="3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D914" s="3" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B915" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C915" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D915" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B916" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C916" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D916" s="3" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B917" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C917" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D917" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B918" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C918" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D918" s="3" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B919" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C919" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D919" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B920" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C920" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D920" s="3" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B921" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C921" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D921" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B922" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C922" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D922" s="3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B923" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C923" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D923" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B924" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C924" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D924" s="3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B925" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C925" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D925" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B926" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C926" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="D926" s="3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B927" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C927" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D927" s="5" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B928" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C928" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D928" s="3" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B929" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C929" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D929" s="5" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B930" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C930" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D930" s="3" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B931" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C931" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D931" s="5" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B932" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C932" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D932" s="3" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B933" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C933" s="5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D933" s="5" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B934" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C934" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D934" s="3" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B935" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C935" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D935" s="5" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B936" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C936" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D936" s="3" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B937" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C937" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D937" s="5" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B938" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C938" s="3" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="D938" s="3" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B939" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C939" s="5" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="D939" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B940" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C940" s="3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="D940" s="3" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B941" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C941" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D941" s="5" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B942" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C942" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="D942" s="3" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B943" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C943" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D943" s="5" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B944" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C944" s="3" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="D944" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B945" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C945" s="5" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D945" s="5" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B946" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C946" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="D946" s="3" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B947" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C947" s="5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D947" s="5" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B948" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C948" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="D948" s="3" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B949" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C949" s="5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D949" s="5" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B950" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C950" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D950" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B951" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C951" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D951" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B952" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C952" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D952" s="3" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B953" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C953" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D953" s="5" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B954" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C954" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D954" s="3" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B955" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C955" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D955" s="5" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B956" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C956" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D956" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B957" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C957" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D957" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B958" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C958" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D958" s="3" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B959" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C959" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D959" s="5" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B960" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C960" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D960" s="3" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B961" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C961" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D961" s="5" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B962" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C962" s="3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D962" s="3" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B963" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C963" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D963" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B964" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C964" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D964" s="3" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B965" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C965" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D965" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B966" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C966" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D966" s="3" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B967" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C967" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D967" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B968" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C968" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D968" s="3" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B969" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C969" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D969" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B970" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C970" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D970" s="3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B971" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C971" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D971" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B972" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C972" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D972" s="3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B973" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C973" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D973" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B974" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C974" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="D974" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B975" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C975" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D975" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B976" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C976" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D976" s="3" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B977" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C977" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D977" s="5" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B978" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C978" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="D978" s="3" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B979" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C979" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D979" s="5" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B980" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C980" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D980" s="3" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B981" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C981" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D981" s="5" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B982" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C982" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D982" s="3" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B983" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C983" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D983" s="5" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B984" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C984" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D984" s="3" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B985" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C985" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D985" s="5" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B986" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C986" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D986" s="3" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B987" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C987" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D987" s="5" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B988" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C988" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D988" s="3" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B989" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C989" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D989" s="5" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B990" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C990" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D990" s="3" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B991" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C991" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D991" s="5" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B992" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C992" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D992" s="3" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B993" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C993" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="D993" s="5" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B994" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C994" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D994" s="3" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B995" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C995" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D995" s="5" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B996" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C996" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D996" s="3" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B997" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C997" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D997" s="5" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D865"/>
+  <autoFilter ref="A1:D997"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/result/szenarien_pivot.xlsx
+++ b/result/szenarien_pivot.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$997</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$1081</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D997"/>
+  <dimension ref="A1:D1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18433,8 +18433,1520 @@
         <v>1.91</v>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B998" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C998" s="3" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="D998" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B999" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C999" s="5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D999" s="5" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1000" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1000" s="3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="D1000" s="3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1001" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1001" s="5" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D1001" s="5" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1002" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1002" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D1002" s="3" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1003" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1003" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="D1003" s="5" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1004" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1004" s="3" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D1004" s="3" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1005" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1005" s="5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="D1005" s="5" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1006" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1006" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="D1006" s="3" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1007" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1007" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D1007" s="5" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1008" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1008" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D1008" s="3" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1009" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1009" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D1009" s="5" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1010" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1010" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D1010" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1011" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1011" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D1011" s="5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1012" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1012" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D1012" s="3" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1013" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1013" s="5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D1013" s="5" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1014" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1014" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D1014" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1015" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1015" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D1015" s="5" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1016" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1016" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D1016" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1017" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1017" s="5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D1017" s="5" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1018" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1018" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D1018" s="3" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1019" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1019" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D1019" s="5" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1020" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1020" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D1020" s="3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1021" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1021" s="5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D1021" s="5" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1022" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1022" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D1022" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1023" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1023" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D1023" s="5" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1024" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1024" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D1024" s="3" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1025" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1025" s="5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D1025" s="5" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1026" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1026" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D1026" s="3" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1027" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1027" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D1027" s="5" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1028" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1028" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="D1028" s="3" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1029" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1029" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D1029" s="5" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1030" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1030" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D1030" s="3" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1031" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1031" s="5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D1031" s="5" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1032" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1032" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="D1032" s="3" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1033" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1033" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D1033" s="5" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1034" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1034" s="3" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="D1034" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1035" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1035" s="5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="D1035" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1036" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1036" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="D1036" s="3" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1037" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1037" s="5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="D1037" s="5" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1038" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1038" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D1038" s="3" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1039" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1039" s="5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D1039" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1040" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1040" s="3" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="D1040" s="3" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1041" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1041" s="5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="D1041" s="5" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1042" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1042" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D1042" s="3" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1043" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1043" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D1043" s="5" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1044" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1044" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D1044" s="3" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1045" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1045" s="5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D1045" s="5" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1046" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1046" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="D1046" s="3" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1047" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1047" s="5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D1047" s="5" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1048" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1048" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D1048" s="3" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1049" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1049" s="5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D1049" s="5" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1050" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1050" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D1050" s="3" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1051" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1051" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D1051" s="5" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1052" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1052" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D1052" s="3" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1053" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1053" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="D1053" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1054" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1054" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D1054" s="3" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1055" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1055" s="5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D1055" s="5" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1056" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1056" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D1056" s="3" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1057" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1057" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D1057" s="5" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1058" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1058" s="3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="D1058" s="3" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1059" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1059" s="5" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="D1059" s="5" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1060" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1060" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D1060" s="3" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1061" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1061" s="5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D1061" s="5" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1062" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1062" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="D1062" s="3" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1063" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1063" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D1063" s="5" t="n">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1064" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1064" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="D1064" s="3" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1065" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1065" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D1065" s="5" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1066" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1066" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D1066" s="3" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1067" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1067" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D1067" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1068" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1068" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D1068" s="3" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1069" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1069" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="D1069" s="5" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1070" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1070" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D1070" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1071" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1071" s="5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="D1071" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1072" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1072" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D1072" s="3" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1073" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1073" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D1073" s="5" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1074" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1074" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D1074" s="3" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1075" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1075" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D1075" s="5" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1076" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1076" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D1076" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1077" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1077" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D1077" s="5" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1078" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1078" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1078" s="3" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1079" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1079" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1079" s="5" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1080" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1080" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D1080" s="3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1081" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1081" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D1081" s="5" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D997"/>
+  <autoFilter ref="A1:D1081"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/result/szenarien_pivot.xlsx
+++ b/result/szenarien_pivot.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$1081</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$1273</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1081"/>
+  <dimension ref="A1:D1273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19945,8 +19945,3464 @@
         <v>2.11</v>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1082" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1082" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D1082" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1083" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1083" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1083" s="5" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1084" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1084" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D1084" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1085" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1085" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D1085" s="5" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1086" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1086" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D1086" s="3" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1087" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1087" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D1087" s="5" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1088" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1088" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D1088" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1089" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1089" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D1089" s="5" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1090" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1090" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D1090" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1091" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1091" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D1091" s="5" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1092" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1092" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D1092" s="3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1093" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1093" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D1093" s="5" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1094" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1094" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D1094" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1095" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1095" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D1095" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1096" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1096" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D1096" s="3" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1097" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1097" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D1097" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1098" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1098" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D1098" s="3" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1099" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1099" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D1099" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1100" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1100" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D1100" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1101" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1101" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D1101" s="5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1102" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1102" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1102" s="3" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1103" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1103" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1103" s="5" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1104" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1104" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1104" s="3" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1105" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1105" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1105" s="5" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1106" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1106" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D1106" s="3" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1107" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1107" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="D1107" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1108" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1108" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D1108" s="3" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1109" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1109" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D1109" s="5" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1110" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1110" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D1110" s="3" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1111" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1111" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D1111" s="5" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1112" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1112" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D1112" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1113" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1113" s="5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D1113" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1114" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1114" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D1114" s="3" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1115" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1115" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D1115" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1116" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1116" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D1116" s="3" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1117" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1117" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D1117" s="5" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1118" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1118" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D1118" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1119" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1119" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D1119" s="5" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1120" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1120" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D1120" s="3" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1121" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1121" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D1121" s="5" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1122" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1122" s="3" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1123" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1123" s="5" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1124" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1124" s="3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="D1124" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1125" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1125" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D1125" s="5" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1126" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1126" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D1126" s="3" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1127" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1127" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D1127" s="5" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1128" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1128" s="3" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1129" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1129" s="5" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1130" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1130" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1130" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1131" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1131" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D1131" s="5" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1132" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1132" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D1132" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1133" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1133" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D1133" s="5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1134" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1134" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D1134" s="3" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1135" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1135" s="5" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1136" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1136" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D1136" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1137" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1137" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D1137" s="5" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1138" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1138" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D1138" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1139" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1139" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D1139" s="5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1140" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1140" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D1140" s="3" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1141" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1141" s="5" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1142" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1142" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D1142" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1143" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1143" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D1143" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1144" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1144" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D1144" s="3" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1145" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1145" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D1145" s="5" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1146" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1146" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D1146" s="3" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1147" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1147" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D1147" s="5" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1148" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1148" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D1148" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1149" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1149" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D1149" s="5" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1150" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1150" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D1150" s="3" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1151" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1151" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D1151" s="5" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1152" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1152" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D1152" s="3" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1153" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1153" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D1153" s="5" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1154" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1154" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D1154" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1155" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1155" s="5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="D1155" s="5" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1156" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1156" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="D1156" s="3" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1157" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1157" s="5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="D1157" s="5" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1158" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1158" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="D1158" s="3" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1159" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1159" s="5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="D1159" s="5" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1160" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1160" s="3" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="D1160" s="3" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1161" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1161" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D1161" s="5" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1162" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1162" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="D1162" s="3" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1163" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1163" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D1163" s="5" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1164" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1164" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D1164" s="3" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1165" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1165" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D1165" s="5" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1166" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1166" s="3" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D1166" s="3" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1167" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1167" s="5" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D1167" s="5" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1168" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1168" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="D1168" s="3" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1169" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1169" s="5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D1169" s="5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1170" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1170" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D1170" s="3" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1171" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1171" s="5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D1171" s="5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1172" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1172" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D1172" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1173" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1173" s="5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="D1173" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1174" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1174" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D1174" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1175" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1175" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D1175" s="5" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1176" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1176" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D1176" s="3" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1177" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1177" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D1177" s="5" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1178" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1178" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D1178" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1179" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1179" s="5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D1179" s="5" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1180" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1180" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="D1180" s="3" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1181" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1181" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D1181" s="5" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1182" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1182" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D1182" s="3" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1183" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1183" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D1183" s="5" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1184" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1184" s="3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D1184" s="3" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1185" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1185" s="5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="D1185" s="5" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1186" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1186" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D1186" s="3" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1187" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1187" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D1187" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1188" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1188" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D1188" s="3" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1189" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1189" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D1189" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1190" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1190" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D1190" s="3" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1191" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1191" s="5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D1191" s="5" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1192" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1192" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D1192" s="3" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1193" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1193" s="5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D1193" s="5" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1194" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1194" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D1194" s="3" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1195" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1195" s="5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D1195" s="5" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1196" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1196" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D1196" s="3" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1197" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1197" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D1197" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1198" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1198" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D1198" s="3" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1199" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1199" s="5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="D1199" s="5" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1200" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1200" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1200" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1201" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1201" s="5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="D1201" s="5" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1202" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1202" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D1202" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1203" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1203" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D1203" s="5" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1204" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1204" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D1204" s="3" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1205" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1205" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D1205" s="5" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1206" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1206" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D1206" s="3" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1207" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1207" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D1207" s="5" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1208" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1208" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D1208" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1209" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1209" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1209" s="5" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1210" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1210" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D1210" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1211" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1211" s="5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D1211" s="5" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1212" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1212" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D1212" s="3" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1213" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1213" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D1213" s="5" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1214" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1214" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D1214" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1215" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1215" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="D1215" s="5" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1216" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1216" s="3" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D1216" s="3" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1217" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1217" s="5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D1217" s="5" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1218" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1218" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D1218" s="3" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1219" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1219" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D1219" s="5" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1220" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1220" s="3" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="D1220" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1221" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1221" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D1221" s="5" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1222" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1222" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="D1222" s="3" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1223" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1223" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D1223" s="5" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1224" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1224" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D1224" s="3" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1225" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1225" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D1225" s="5" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1226" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1226" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D1226" s="3" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1227" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1227" s="5" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="D1227" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1228" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1229" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1229" s="5" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="D1229" s="5" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1230" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1230" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D1230" s="3" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1231" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1231" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D1231" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1232" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1232" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1232" s="3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1233" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1233" s="5" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="D1233" s="5" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1234" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1234" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1234" s="3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1235" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1235" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1235" s="5" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1236" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1236" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="D1236" s="3" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1237" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1237" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="D1237" s="5" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1238" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1238" s="3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="D1238" s="3" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1239" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1239" s="5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="D1239" s="5" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1240" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1240" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D1240" s="3" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1241" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1241" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D1241" s="5" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1242" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1242" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D1242" s="3" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1243" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1243" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D1243" s="5" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1244" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1244" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D1244" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1245" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1245" s="5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="D1245" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1246" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1246" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D1246" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1247" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1247" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D1247" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1248" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1248" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="D1248" s="3" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1249" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1249" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D1249" s="5" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1250" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1250" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D1250" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1251" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1251" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D1251" s="5" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1252" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1252" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="D1252" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1253" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1253" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="D1253" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1254" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1254" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D1254" s="3" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1255" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1255" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D1255" s="5" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1256" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1256" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D1256" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1257" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1257" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D1257" s="5" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1258" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1258" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D1258" s="3" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1259" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1259" s="5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D1259" s="5" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1260" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1260" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D1260" s="3" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1261" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1261" s="5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D1261" s="5" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1262" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1262" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="D1262" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1263" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1263" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D1263" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1264" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1264" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D1264" s="3" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1265" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1265" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D1265" s="5" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1266" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1266" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D1266" s="3" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1267" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1267" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D1267" s="5" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1268" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1268" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="D1268" s="3" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1269" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1269" s="5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="D1269" s="5" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1270" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1270" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D1270" s="3" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1271" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1271" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="D1271" s="5" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1272" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1272" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D1272" s="3" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1273" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1273" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D1273" s="5" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1081"/>
+  <autoFilter ref="A1:D1273"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/result/szenarien_pivot.xlsx
+++ b/result/szenarien_pivot.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$1273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daten'!$A$1:$D$1441</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1273"/>
+  <dimension ref="A1:D1441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23401,8 +23401,3032 @@
         <v>2.01</v>
       </c>
     </row>
+    <row r="1274">
+      <c r="A1274" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1274" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1274" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="D1274" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1275" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1275" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="D1275" s="5" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1276" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1276" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="D1276" s="3" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1277" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1277" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D1277" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1278" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1278" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D1278" s="3" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1279" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1279" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D1279" s="5" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1280" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1280" s="3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D1280" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1281" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1281" s="5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="D1281" s="5" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1282" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1282" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D1282" s="3" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1283" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1283" s="5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D1283" s="5" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1284" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1284" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D1284" s="3" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1285" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1285" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D1285" s="5" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1286" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1286" s="3" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="D1286" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1287" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1287" s="5" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="D1287" s="5" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1288" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1288" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D1288" s="3" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1289" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1289" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="D1289" s="5" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1290" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1290" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D1290" s="3" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1291" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1291" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="D1291" s="5" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1292" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1292" s="3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="D1292" s="3" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1293" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1293" s="5" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="D1293" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1294" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1294" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D1294" s="3" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1295" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1295" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D1295" s="5" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1296" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1296" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="D1296" s="3" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1297" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1297" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D1297" s="5" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1298" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1298" s="3" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="D1298" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1299" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1299" s="5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D1299" s="5" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1300" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1300" s="3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D1300" s="3" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1301" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1301" s="5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D1301" s="5" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1302" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1302" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1302" s="3" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1303" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1303" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D1303" s="5" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1304" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1304" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D1304" s="3" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1305" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1305" s="5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="D1305" s="5" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1306" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1306" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D1306" s="3" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1307" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1307" s="5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D1307" s="5" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1308" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1308" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D1308" s="3" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1309" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1309" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D1309" s="5" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1310" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1310" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="D1310" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1311" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1311" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D1311" s="5" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1312" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1312" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="D1312" s="3" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1313" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1313" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D1313" s="5" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1314" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1314" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D1314" s="3" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1315" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1315" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D1315" s="5" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1316" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1316" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="D1316" s="3" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1317" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1317" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D1317" s="5" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1318" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1318" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D1318" s="3" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1319" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1319" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D1319" s="5" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1320" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1320" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D1320" s="3" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1321" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1321" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D1321" s="5" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1322" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1322" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="D1322" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1323" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1323" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D1323" s="5" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1324" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1324" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D1324" s="3" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1325" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1325" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D1325" s="5" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1326" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1326" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D1326" s="3" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1327" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1327" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D1327" s="5" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1328" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1328" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D1328" s="3" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1329" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1329" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D1329" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1330" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1330" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D1330" s="3" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1331" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1331" s="5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="D1331" s="5" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1332" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1332" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D1332" s="3" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1333" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1333" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D1333" s="5" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1334" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1334" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="D1334" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1335" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1335" s="5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="D1335" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1336" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1336" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="D1336" s="3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1337" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1337" s="5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D1337" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1338" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1338" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D1338" s="3" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1339" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1339" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D1339" s="5" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1340" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1340" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D1340" s="3" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1341" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1341" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D1341" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1342" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1342" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D1342" s="3" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1343" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1343" s="5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D1343" s="5" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1344" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1344" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D1344" s="3" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1345" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1345" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D1345" s="5" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1346" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1346" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D1346" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1347" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1347" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D1347" s="5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1348" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1348" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D1348" s="3" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1349" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1349" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D1349" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1350" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1350" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D1350" s="3" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1351" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1351" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D1351" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1352" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1352" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D1352" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1353" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1353" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D1353" s="5" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1354" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1354" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D1354" s="3" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1355" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1355" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D1355" s="5" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1356" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1356" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D1356" s="3" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1357" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1357" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D1357" s="5" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1358" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1358" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D1358" s="3" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1359" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1359" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D1359" s="5" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1360" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1360" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D1360" s="3" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1361" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1361" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D1361" s="5" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1362" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1362" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D1362" s="3" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1363" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1363" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D1363" s="5" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1364" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1364" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D1364" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1365" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1365" s="5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="D1365" s="5" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1366" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1366" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D1366" s="3" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1367" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1367" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D1367" s="5" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1368" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1368" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D1368" s="3" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1369" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1369" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D1369" s="5" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1370" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1370" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D1370" s="3" t="n">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1371" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1371" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D1371" s="5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1372" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1372" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1372" s="3" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1373" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1373" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1373" s="5" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1374" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1374" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1374" s="3" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1375" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1375" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1375" s="5" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1376" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1376" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D1376" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1377" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1377" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D1377" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1378" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1378" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1378" s="3" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1379" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1379" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1379" s="5" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1380" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1380" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1380" s="3" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1381" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1381" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1381" s="5" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1382" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1382" s="3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D1382" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1383" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1383" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D1383" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1384" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1384" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D1384" s="3" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1385" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1385" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D1385" s="5" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1386" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1386" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D1386" s="3" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1387" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1387" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D1387" s="5" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1388" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1388" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D1388" s="3" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1389" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1389" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D1389" s="5" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1390" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1390" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D1390" s="3" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1391" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1391" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D1391" s="5" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1392" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1392" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D1392" s="3" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1393" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1393" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D1393" s="5" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1394" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1394" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D1394" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1395" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1395" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D1395" s="5" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1396" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1396" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D1396" s="3" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1397" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1397" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D1397" s="5" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1398" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1398" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D1398" s="3" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1399" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1399" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D1399" s="5" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1400" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1400" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D1400" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1401" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1401" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D1401" s="5" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1402" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1402" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D1402" s="3" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1403" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1403" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D1403" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1404" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1404" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D1404" s="3" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1405" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1405" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D1405" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1406" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1406" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="D1406" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1407" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1407" s="5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="D1407" s="5" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1408" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1408" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D1408" s="3" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1409" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1409" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D1409" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1410" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1410" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D1410" s="3" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1411" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1411" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D1411" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1412" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1412" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="D1412" s="3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1413" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1413" s="5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="D1413" s="5" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1414" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1414" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D1414" s="3" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1415" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1415" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D1415" s="5" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1416" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1416" s="3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D1416" s="3" t="n">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1417" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1417" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D1417" s="5" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1418" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1418" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="D1418" s="3" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1419" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1419" s="5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D1419" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1420" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1420" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D1420" s="3" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1421" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1421" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D1421" s="5" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1422" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1422" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D1422" s="3" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1423" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1423" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D1423" s="5" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1424" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1424" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="D1424" s="3" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1425" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1425" s="5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D1425" s="5" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1426" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1426" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D1426" s="3" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1427" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1427" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D1427" s="5" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1428" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1428" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D1428" s="3" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1429" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1429" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D1429" s="5" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1430" s="2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C1430" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="D1430" s="3" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1431" s="4" t="inlineStr">
+        <is>
+          <t>sz01</t>
+        </is>
+      </c>
+      <c r="C1431" s="5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="D1431" s="5" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1432" s="2" t="inlineStr">
+        <is>
+          <t>sz02</t>
+        </is>
+      </c>
+      <c r="C1432" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D1432" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1433" s="4" t="inlineStr">
+        <is>
+          <t>sz03</t>
+        </is>
+      </c>
+      <c r="C1433" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D1433" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1434" s="2" t="inlineStr">
+        <is>
+          <t>sz04</t>
+        </is>
+      </c>
+      <c r="C1434" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D1434" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1435" s="4" t="inlineStr">
+        <is>
+          <t>sz05</t>
+        </is>
+      </c>
+      <c r="C1435" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D1435" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1436" s="2" t="inlineStr">
+        <is>
+          <t>sz06</t>
+        </is>
+      </c>
+      <c r="C1436" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="D1436" s="3" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1437" s="4" t="inlineStr">
+        <is>
+          <t>sz07</t>
+        </is>
+      </c>
+      <c r="C1437" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D1437" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1438" s="2" t="inlineStr">
+        <is>
+          <t>sz08</t>
+        </is>
+      </c>
+      <c r="C1438" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D1438" s="3" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1439" s="4" t="inlineStr">
+        <is>
+          <t>sz09</t>
+        </is>
+      </c>
+      <c r="C1439" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D1439" s="5" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1440" s="2" t="inlineStr">
+        <is>
+          <t>sz10</t>
+        </is>
+      </c>
+      <c r="C1440" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D1440" s="3" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1441" s="4" t="inlineStr">
+        <is>
+          <t>sz11</t>
+        </is>
+      </c>
+      <c r="C1441" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D1441" s="5" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1273"/>
+  <autoFilter ref="A1:D1441"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
